--- a/results/Int All Data -0.6/Linea_fi_all.xlsx
+++ b/results/Int All Data -0.6/Linea_fi_all.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-9.168704156479191e-05 +/- 0.000433296053751766</t>
+          <t>-0.00012224938875305958 +/- 0.00043651763010653144</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.0025656148628722788 +/- 0.0017597792683970272</t>
+          <t>-0.002536125036862258 +/- 0.0017154868265702352</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.03415211601065406 +/- 0.0020124297129328235</t>
+          <t>0.034181710565256006 +/- 0.0020428819006122916</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
+          <t>-0.00011837821840781082 +/- 0.0013115430486037253</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
           <t>-8.878366380585812e-05 +/- 0.001350043767736826</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-0.00011837821840781082 +/- 0.0013115430486037253</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.0005022156573116998 +/- 0.0017579409804209286</t>
+          <t>0.0005317577548006214 +/- 0.0017911381259940193</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.008335944844876163 +/- 0.00216754828778321</t>
+          <t>0.008367282983390734 +/- 0.0021440875566402155</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="DX10" t="inlineStr">
         <is>
-          <t>0.004177470469605293 +/- 0.001309198244598295</t>
+          <t>0.004206280610774993 +/- 0.001334005981306854</t>
         </is>
       </c>
       <c r="DY10" t="inlineStr">
